--- a/BWI/bestwine_output/bestwine_Georgia.xlsx
+++ b/BWI/bestwine_output/bestwine_Georgia.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA30"/>
+  <dimension ref="A1:AA32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -3653,6 +3653,208 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Carrefour Georgia</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Carrefour Georgia</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>106508</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>T'bilisi</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Tbilisi</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>16 Davit Aghmashenebeli Avenue</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr"/>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.carrefour.ge</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr"/>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>mobappgeo@mafcarrefour.com</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>+995 32 217 70 70</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/CarrefourGeorgia/</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/carrefour_georgia/</t>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr"/>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCQ7aPJ3odUD15oPgBrqhEtA</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>Ekaterine Pilauri</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>Beverages  Merchandise Manager</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr"/>
+      <c r="Z31" s="2" t="inlineStr"/>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ekaterine-pilauri-28916935/</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Carrefour Georgia</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Carrefour Georgia</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>106508</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>T'bilisi</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Tbilisi</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>16 Davit Aghmashenebeli Avenue</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr"/>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.carrefour.ge</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr"/>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>mobappgeo@mafcarrefour.com</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>+995 32 217 70 70</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/CarrefourGeorgia/</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/carrefour_georgia/</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr"/>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCQ7aPJ3odUD15oPgBrqhEtA</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>Giorgi Gobejishvili</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>Business Development Director</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr"/>
+      <c r="Z32" s="2" t="inlineStr"/>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/giorgi-gobejishvili-036896103/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
